--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1885.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6442AA-CFEA-486B-852A-A236A8FA63A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB55CC7-81E2-4BB0-B460-640C4AFE59CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{51AF7A87-2DFB-4345-A704-45D3AE345F30}"/>
   </bookViews>
@@ -291,9 +291,6 @@
     <t>р YY</t>
   </si>
   <si>
-    <t>c YY</t>
-  </si>
-  <si>
     <t>чу YY</t>
   </si>
   <si>
@@ -348,9 +345,6 @@
     <t>Севастополь -- в т.ч. кваритрующих войск 9,044</t>
   </si>
   <si>
-    <t>Всего</t>
-  </si>
-  <si>
     <t>Астраханская (оседлое)</t>
   </si>
   <si>
@@ -385,6 +379,12 @@
   </si>
   <si>
     <t>Забайкальская</t>
+  </si>
+  <si>
+    <t>с YY</t>
+  </si>
+  <si>
+    <t>Всего Империя</t>
   </si>
 </sst>
 </file>
@@ -468,11 +468,11 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,32 +812,32 @@
   <sheetData>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -878,46 +878,46 @@
         <v>82</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>83</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I1" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
@@ -958,7 +958,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B4" s="1">
         <v>448100</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B5" s="1">
         <v>347512</v>
@@ -3308,22 +3308,22 @@
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B70" s="14">
+      <c r="B70" s="13">
         <v>90182878</v>
       </c>
-      <c r="C70" s="14">
+      <c r="C70" s="13">
         <v>4324169</v>
       </c>
-      <c r="D70" s="14">
+      <c r="D70" s="13">
         <v>3096415</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="15">
         <v>4.79</v>
       </c>
-      <c r="F70" s="16">
+      <c r="F70" s="15">
         <v>3.43</v>
       </c>
       <c r="G70" s="7"/>
@@ -3367,9 +3367,11 @@
         <f>F70-M70</f>
         <v>-3.4843472172179091E-3</v>
       </c>
-      <c r="U70" s="12" t="s">
-        <v>106</v>
-      </c>
+      <c r="U70" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="V70" s="16"/>
+      <c r="W70" s="16"/>
       <c r="Y70" s="1">
         <f>O70+B5</f>
         <v>1000</v>
@@ -3452,25 +3454,25 @@
         <v>68</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G74" s="2"/>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B75" s="1">
         <v>80000</v>
@@ -3482,10 +3484,10 @@
         <v>189</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G75" s="2"/>
       <c r="L75" s="6">
@@ -3502,19 +3504,19 @@
         <v>69</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G76" s="2"/>
     </row>
@@ -3562,16 +3564,16 @@
         <v>1212600</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G78" s="2"/>
     </row>
@@ -3652,19 +3654,19 @@
         <v>74</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G81" s="2"/>
     </row>
@@ -3715,8 +3717,8 @@
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="12" t="s">
-        <v>107</v>
+      <c r="A84" s="16" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -3727,16 +3729,16 @@
         <v>36492</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G85" s="2"/>
     </row>
@@ -3771,11 +3773,11 @@
         <v>3.36267363498831</v>
       </c>
       <c r="R86" s="6">
-        <f>E86-L86</f>
+        <f t="shared" ref="R86:S88" si="6">E86-L86</f>
         <v>-5.1753541466097452E-2</v>
       </c>
       <c r="S86" s="6">
-        <f>F86-M86</f>
+        <f t="shared" si="6"/>
         <v>-6.2673634988310134E-2</v>
       </c>
     </row>
@@ -3810,11 +3812,11 @@
         <v>2.8902695676395038</v>
       </c>
       <c r="R87" s="6">
-        <f>E87-L87</f>
+        <f t="shared" si="6"/>
         <v>-6.0706880009903319E-2</v>
       </c>
       <c r="S87" s="6">
-        <f>F87-M87</f>
+        <f t="shared" si="6"/>
         <v>-9.0269567639504E-2</v>
       </c>
     </row>
@@ -3849,17 +3851,17 @@
         <v>2.5491966977471923</v>
       </c>
       <c r="R88" s="6">
-        <f>E88-L88</f>
+        <f t="shared" si="6"/>
         <v>-2.4409448818897062E-2</v>
       </c>
       <c r="S88" s="6">
-        <f>F88-M88</f>
+        <f t="shared" si="6"/>
         <v>-4.9196697747192264E-2</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B90" s="1">
         <v>72000</v>
@@ -3894,16 +3896,16 @@
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B92" s="14">
+      <c r="A92" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B92" s="13">
         <v>94243304</v>
       </c>
-      <c r="C92" s="14"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="13"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
       <c r="I92" s="10">
         <f>SUM(B72:B90) +I70</f>
         <v>94589816</v>
@@ -3912,9 +3914,11 @@
         <f>B92-I92</f>
         <v>-346512</v>
       </c>
-      <c r="U92" s="12" t="s">
-        <v>106</v>
-      </c>
+      <c r="U92" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="V92" s="16"/>
+      <c r="W92" s="16"/>
       <c r="Y92" s="1">
         <f>O92+B5</f>
         <v>1000</v>
@@ -3922,10 +3926,10 @@
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C94" s="1">
         <v>949</v>
@@ -3939,10 +3943,10 @@
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C95" s="1">
         <v>3176</v>
@@ -3956,10 +3960,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C97" s="1">
         <v>21019</v>
@@ -3973,7 +3977,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B98" s="2">
         <v>530896</v>
@@ -3985,7 +3989,7 @@
         <v>16474</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1885.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1885.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB55CC7-81E2-4BB0-B460-640C4AFE59CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CE521E-255A-43F4-A687-6F913C038E70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{51AF7A87-2DFB-4345-A704-45D3AE345F30}"/>
+    <workbookView xWindow="17085" yWindow="3705" windowWidth="19785" windowHeight="18390" activeTab="1" xr2:uid="{51AF7A87-2DFB-4345-A704-45D3AE345F30}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
     <sheet name="Data" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,12 +24,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="123">
   <si>
     <t>Архангельская</t>
   </si>
@@ -385,6 +380,27 @@
   </si>
   <si>
     <t>Всего Империя</t>
+  </si>
+  <si>
+    <t>Область войска Донского</t>
+  </si>
+  <si>
+    <t>Область войска Донского по</t>
+  </si>
+  <si>
+    <t>"Движение населения в Европейской России за 1885 год" стр. 4</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>"Сборник сведений по России 1884-1885", стр. 28-33</t>
+  </si>
+  <si>
+    <t>1-й источник</t>
+  </si>
+  <si>
+    <t>2-й источник</t>
   </si>
 </sst>
 </file>
@@ -394,7 +410,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -473,6 +489,7 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -808,34 +825,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{359DB130-2733-42E7-A7E1-BFED63FFB798}">
   <dimension ref="A3:A12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>101</v>
       </c>
@@ -847,27 +864,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE36C87A-2E95-471F-B425-C083DF5337A3}">
-  <dimension ref="A1:Y98"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:Y111"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="29.05078125" customWidth="1"/>
-    <col min="2" max="2" width="9.9453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" customWidth="1"/>
+    <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="4.41796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.20703125" style="6" customWidth="1"/>
-    <col min="9" max="9" width="9.9453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.15625" customWidth="1"/>
+    <col min="5" max="6" width="4.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.25" style="6" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" customWidth="1"/>
     <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="5.83984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.89453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.05078125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.26171875" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.15625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:19" ht="15">
       <c r="A1" s="3" t="s">
         <v>80</v>
       </c>
@@ -920,7 +937,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -956,7 +973,7 @@
         <v>-1.5840563004307917E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -992,7 +1009,7 @@
         <v>-9.2189243472438953E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -1000,7 +1017,7 @@
         <v>347512</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:19">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1036,7 +1053,7 @@
         <v>-8.9454627572451262E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:19">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1072,7 +1089,7 @@
         <v>-3.8731653309261649E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:19">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1108,7 +1125,7 @@
         <v>-3.3962543763777386E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:19">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1144,7 +1161,7 @@
         <v>-8.0064809063022491E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:19">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1180,7 +1197,7 @@
         <v>-8.9960806397844095E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:19">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1216,7 +1233,7 @@
         <v>-7.1474482185967858E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:19">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1252,7 +1269,7 @@
         <v>-5.2892517368392955E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:19">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1288,7 +1305,7 @@
         <v>-4.7130407618558134E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:19">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1324,7 +1341,7 @@
         <v>-2.9044638940844525E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1360,7 +1377,7 @@
         <v>-3.2508089713584098E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:19">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -1396,7 +1413,7 @@
         <v>-8.2584310784083126E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1432,7 +1449,7 @@
         <v>-1.1030125710216332E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1468,7 +1485,7 @@
         <v>-8.4832109082124685E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:19">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -1504,7 +1521,7 @@
         <v>-9.1285615555413813E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1540,7 +1557,7 @@
         <v>-7.8591502082794751E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1576,7 +1593,7 @@
         <v>-7.3718053512069837E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1612,7 +1629,7 @@
         <v>-6.6286543998595349E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -1648,7 +1665,7 @@
         <v>-8.2736191501720846E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1684,7 +1701,7 @@
         <v>-8.7224443541662033E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -1720,7 +1737,7 @@
         <v>-3.6426367546699812E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -1756,7 +1773,7 @@
         <v>-1.5258515214009893E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:19">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -1792,7 +1809,7 @@
         <v>-3.2009799207024514E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -1828,7 +1845,7 @@
         <v>-1.1945250556885334E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -1864,7 +1881,7 @@
         <v>-3.4847324483802566E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:19">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1900,7 +1917,7 @@
         <v>-4.2312023146488631E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:19">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1936,7 +1953,7 @@
         <v>-9.0553724107155453E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1972,7 +1989,7 @@
         <v>-2.2506659538858997E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:19">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -2008,7 +2025,7 @@
         <v>-3.3453031937002997E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:19">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -2045,7 +2062,7 @@
         <v>-1.4002013202141228E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:19">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -2081,7 +2098,7 @@
         <v>-9.868820084170693E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:19">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -2117,7 +2134,7 @@
         <v>-3.6414279890930601E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:19">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -2153,7 +2170,7 @@
         <v>-5.2797809800352979E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:19">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -2189,7 +2206,7 @@
         <v>-5.0419233964226429E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:19">
       <c r="A39" t="s">
         <v>34</v>
       </c>
@@ -2225,7 +2242,7 @@
         <v>-3.7457859074067734E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
         <v>35</v>
       </c>
@@ -2261,7 +2278,7 @@
         <v>-2.0776895874102586E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:19">
       <c r="A41" t="s">
         <v>36</v>
       </c>
@@ -2297,7 +2314,7 @@
         <v>-4.72354641798578E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:19">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -2333,7 +2350,7 @@
         <v>-8.7863179761532351E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:19">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -2369,7 +2386,7 @@
         <v>-5.3033845835118498E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -2405,7 +2422,7 @@
         <v>-9.0775640445054595E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:19">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -2441,7 +2458,7 @@
         <v>-9.9243289760671871E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:19">
       <c r="A46" t="s">
         <v>41</v>
       </c>
@@ -2477,7 +2494,7 @@
         <v>-4.3422444465814447E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -2513,7 +2530,7 @@
         <v>-2.2075136601857892E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:19">
       <c r="A48" t="s">
         <v>43</v>
       </c>
@@ -2549,7 +2566,7 @@
         <v>-9.6901867228761152E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:19">
       <c r="A49" t="s">
         <v>44</v>
       </c>
@@ -2585,7 +2602,7 @@
         <v>-2.1847585414389137E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:19">
       <c r="A50" t="s">
         <v>45</v>
       </c>
@@ -2621,7 +2638,7 @@
         <v>-4.8672275162492618E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:19">
       <c r="A51" t="s">
         <v>46</v>
       </c>
@@ -2657,7 +2674,7 @@
         <v>-4.6636396879947029E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:19">
       <c r="A52" t="s">
         <v>47</v>
       </c>
@@ -2694,7 +2711,7 @@
         <v>-1.1342686603901253E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:19">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -2730,7 +2747,7 @@
         <v>2.3077468079164554E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:19">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -2766,7 +2783,7 @@
         <v>0.29544326930503573</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:19">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -2802,7 +2819,7 @@
         <v>-2.7617932288442226E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:19">
       <c r="A56" t="s">
         <v>51</v>
       </c>
@@ -2838,7 +2855,7 @@
         <v>-9.0957909247669111E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:19">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -2874,7 +2891,7 @@
         <v>-2.1031997623226495E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:19">
       <c r="A58" t="s">
         <v>53</v>
       </c>
@@ -2910,7 +2927,7 @@
         <v>-1.1225903993952624E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
         <v>54</v>
       </c>
@@ -2946,7 +2963,7 @@
         <v>-8.9728326286077742E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:19">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -2982,7 +2999,7 @@
         <v>-7.5338659617241177E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:19">
       <c r="A61" t="s">
         <v>56</v>
       </c>
@@ -3018,7 +3035,7 @@
         <v>-9.2133475254533082E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
         <v>57</v>
       </c>
@@ -3054,7 +3071,7 @@
         <v>-2.4757433751510405E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:19">
       <c r="A63" t="s">
         <v>58</v>
       </c>
@@ -3091,7 +3108,7 @@
         <v>-3.5978189019045814E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:19">
       <c r="A64" t="s">
         <v>59</v>
       </c>
@@ -3127,7 +3144,7 @@
         <v>-5.7022421850072114E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:25">
       <c r="A65" t="s">
         <v>60</v>
       </c>
@@ -3163,7 +3180,7 @@
         <v>-5.2349322522510899E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:25">
       <c r="A66" t="s">
         <v>61</v>
       </c>
@@ -3199,7 +3216,7 @@
         <v>-2.4690619138728831E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:25">
       <c r="A67" t="s">
         <v>62</v>
       </c>
@@ -3235,7 +3252,7 @@
         <v>-2.1051825997326912E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:25">
       <c r="A68" t="s">
         <v>63</v>
       </c>
@@ -3271,7 +3288,7 @@
         <v>-7.8415148215114083E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:25">
       <c r="A69" t="s">
         <v>64</v>
       </c>
@@ -3307,7 +3324,7 @@
         <v>-9.52571662124857E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:25">
       <c r="A70" s="12" t="s">
         <v>65</v>
       </c>
@@ -3377,7 +3394,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:25">
       <c r="A72" t="s">
         <v>66</v>
       </c>
@@ -3413,7 +3430,7 @@
         <v>-9.5908582045623358E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:25">
       <c r="A73" t="s">
         <v>67</v>
       </c>
@@ -3449,7 +3466,7 @@
         <v>-4.6157041960947165E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:25">
       <c r="A74" t="s">
         <v>68</v>
       </c>
@@ -3470,7 +3487,7 @@
       </c>
       <c r="G74" s="2"/>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:25">
       <c r="A75" t="s">
         <v>107</v>
       </c>
@@ -3499,7 +3516,7 @@
         <v>0.23625000000000002</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:25">
       <c r="A76" t="s">
         <v>69</v>
       </c>
@@ -3520,7 +3537,7 @@
       </c>
       <c r="G76" s="2"/>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:25">
       <c r="A77" t="s">
         <v>70</v>
       </c>
@@ -3556,7 +3573,7 @@
         <v>-4.7003552245929114E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:25">
       <c r="A78" t="s">
         <v>71</v>
       </c>
@@ -3577,7 +3594,7 @@
       </c>
       <c r="G78" s="2"/>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:25">
       <c r="A79" t="s">
         <v>72</v>
       </c>
@@ -3613,7 +3630,7 @@
         <v>5.6228313253012052</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:25">
       <c r="A80" t="s">
         <v>73</v>
       </c>
@@ -3649,7 +3666,7 @@
         <v>-1.9547347332548037E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:25">
       <c r="A81" t="s">
         <v>74</v>
       </c>
@@ -3670,7 +3687,7 @@
       </c>
       <c r="G81" s="2"/>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:25">
       <c r="A82" t="s">
         <v>75</v>
       </c>
@@ -3706,7 +3723,7 @@
         <v>-9.5747451329119659E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:25">
       <c r="R83" s="6">
         <f>E83-L83</f>
         <v>0</v>
@@ -3716,12 +3733,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:25">
       <c r="A84" s="16" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:25">
       <c r="A85" t="s">
         <v>76</v>
       </c>
@@ -3742,7 +3759,7 @@
       </c>
       <c r="G85" s="2"/>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:25">
       <c r="A86" t="s">
         <v>77</v>
       </c>
@@ -3781,7 +3798,7 @@
         <v>-6.2673634988310134E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:25">
       <c r="A87" t="s">
         <v>78</v>
       </c>
@@ -3820,7 +3837,7 @@
         <v>-9.0269567639504E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:25">
       <c r="A88" t="s">
         <v>79</v>
       </c>
@@ -3859,7 +3876,7 @@
         <v>-4.9196697747192264E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:25">
       <c r="A90" t="s">
         <v>109</v>
       </c>
@@ -3895,7 +3912,7 @@
         <v>-1.1111111111111294E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:25">
       <c r="A92" s="12" t="s">
         <v>115</v>
       </c>
@@ -3924,7 +3941,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:25">
       <c r="A94" t="s">
         <v>108</v>
       </c>
@@ -3941,7 +3958,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:25">
       <c r="A95" t="s">
         <v>110</v>
       </c>
@@ -3958,7 +3975,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>111</v>
       </c>
@@ -3975,7 +3992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
         <v>112</v>
       </c>
@@ -3990,6 +4007,71 @@
       </c>
       <c r="G98" s="6" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>116</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C101" s="1">
+        <v>95692</v>
+      </c>
+      <c r="D101" s="1">
+        <v>50935</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="B102" s="2"/>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="B103" s="2"/>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="17"/>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>121</v>
+      </c>
+      <c r="C110" s="1">
+        <v>95592</v>
+      </c>
+      <c r="D110" s="1">
+        <v>51035</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>122</v>
+      </c>
+      <c r="C111" s="1">
+        <v>95692</v>
+      </c>
+      <c r="D111" s="1">
+        <v>50935</v>
       </c>
     </row>
   </sheetData>
